--- a/output/pdf_financials_xlsx/MEAT.xlsx
+++ b/output/pdf_financials_xlsx/MEAT.xlsx
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.05771</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.16608</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.069595</v>
       </c>
     </row>
     <row r="35">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.05771</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.16608</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.069595</v>
       </c>
     </row>
     <row r="37">
@@ -1188,13 +1188,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.086576</v>
+        <v>0.028866</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.230152</v>
+        <v>0.064072</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.100151</v>
+        <v>0.030556</v>
       </c>
     </row>
     <row r="49">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">

--- a/output/pdf_financials_xlsx/MEAT.xlsx
+++ b/output/pdf_financials_xlsx/MEAT.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.377105</v>
+        <v>0.603222</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.393226</v>
+        <v>0.704902</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.186123</v>
+        <v>0.447503</v>
       </c>
     </row>
     <row r="8">
@@ -1498,13 +1498,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.126959</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.132335</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.20063</v>
       </c>
     </row>
     <row r="68">
@@ -2859,7 +2859,11 @@
           <t>Intangible assets and goodwill (Notes 9 and 14)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -3477,7 +3481,11 @@
           <t>Intangible assets and goodwill (Notes 10 and 15)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>0.282336</v>
       </c>
@@ -4945,7 +4953,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
         <v>-0.024757</v>
       </c>
@@ -6113,7 +6125,11 @@
           <t>Management and directors’ fees (Note 13)</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -7027,7 +7043,11 @@
           <t>Management and directors’ fees (Note 14)</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E144" s="5" t="n">
         <v>0.226117</v>
       </c>
